--- a/tenable_report.xlsx
+++ b/tenable_report.xlsx
@@ -432,7 +432,7 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Janvier 2024</t>
+          <t>January 2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -619,7 +619,7 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -656,7 +656,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Janvier 2024</t>
+          <t>January 2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Janvier 2024</t>
+          <t>January 2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -794,7 +794,7 @@
   <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -855,7 +855,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Janvier 2024</t>
+          <t>January 2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -902,7 +902,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Janvier 2024</t>
+          <t>January 2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -959,44 +959,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.0.0.6</t>
+          <t>10.0.0.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CVE-2024-0001</t>
+          <t>CVE-2024-0004</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Sec</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.0.0.1</t>
+          <t>10.1.1.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1053,44 +1053,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.0.0.7</t>
+          <t>10.0.0.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CVE-2024-0004</t>
+          <t>CVE-2024-0001</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sec</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.1.1.1</t>
+          <t>10.1.1.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.1.1.1</t>
+          <t>10.1.1.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1194,44 +1194,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.0.0.3</t>
+          <t>10.1.1.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CVE-2024-0001</t>
+          <t>CVE-2024-0004</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Sec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.1.1.2</t>
+          <t>10.0.0.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1288,44 +1288,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.1.1.3</t>
+          <t>10.0.0.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CVE-2024-0001</t>
+          <t>CVE-2024-0004</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Sec</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.1.1.6</t>
+          <t>10.1.1.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1382,44 +1382,44 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10.1.1.7</t>
+          <t>10.1.1.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CVE-2024-0004</t>
+          <t>CVE-2024-0001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sec</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1429,44 +1429,44 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10.0.0.2</t>
+          <t>10.0.0.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CVE-2024-0004</t>
+          <t>CVE-2024-0001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Sec</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1513,7 +1513,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Février 2024</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1560,7 +1560,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1664,44 +1664,44 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.0.0.6</t>
+          <t>10.1.1.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CVE-2024-0001</t>
+          <t>CVE-2024-0004</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Sec</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1711,44 +1711,44 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10.0.0.7</t>
+          <t>10.0.0.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CVE-2024-0004</t>
+          <t>CVE-2024-0001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Sec</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10.1.1.1</t>
+          <t>10.1.1.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.1.1.1</t>
+          <t>10.1.1.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1842,7 +1842,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1852,44 +1852,44 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10.0.0.3</t>
+          <t>10.1.1.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CVE-2024-0001</t>
+          <t>CVE-2024-0004</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Sec</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1899,44 +1899,44 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.0.0.1</t>
+          <t>10.0.0.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CVE-2024-0001</t>
+          <t>CVE-2024-0004</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>Sec</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.1.1.2</t>
+          <t>10.0.0.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10.1.1.3</t>
+          <t>10.0.0.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2030,7 +2030,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10.1.1.6</t>
+          <t>10.1.1.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2077,7 +2077,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2087,44 +2087,44 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10.1.1.7</t>
+          <t>10.1.1.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CVE-2024-0004</t>
+          <t>CVE-2024-0001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sec</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mars 2024</t>
+          <t>March 2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2134,37 +2134,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10.0.0.2</t>
+          <t>10.0.0.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CVE-2024-0004</t>
+          <t>CVE-2024-0001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Sec</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
